--- a/artfynd/A 47608-2022 artfynd.xlsx
+++ b/artfynd/A 47608-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47608-2022 artfynd.xlsx
+++ b/artfynd/A 47608-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>556247</v>
+        <v>61726012</v>
       </c>
       <c r="B2" t="n">
-        <v>88666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1541</v>
+        <v>144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällsopp</t>
+          <t>Stor knopplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Strobilomyces strobilaceus</t>
+          <t>Mycobilimbia pilularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Berk.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Körb.) Hafellner &amp; Türk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vanåsfors norra, Sk</t>
+          <t>Sandsjöholm, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401736.2388778091</v>
+        <v>401830</v>
       </c>
       <c r="R2" t="n">
-        <v>6243500.52955732</v>
+        <v>6243325</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +746,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-09-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-09-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 fruktkropp</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,82 +763,93 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre bokskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvårdsprogram Örkelljunga kommun</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1321735</v>
+        <v>61726010</v>
       </c>
       <c r="B3" t="n">
-        <v>90336</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4786</v>
+        <v>924</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius volemus</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vanåsfors norra, Sk</t>
+          <t>Sandsjöholm, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>401736.2388778091</v>
+        <v>401830</v>
       </c>
       <c r="R3" t="n">
-        <v>6243500.52955732</v>
+        <v>6243325</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,22 +873,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2005-09-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2005-09-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,64 +890,78 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre bokskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvårdsprogram Örkelljunga kommun</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61726012</v>
+        <v>61726011</v>
       </c>
       <c r="B4" t="n">
-        <v>78005</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>144</v>
+        <v>1342</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor knopplav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mycobilimbia pilularis</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Körb.) Hafellner &amp; Türk</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med perithecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -978,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>401829.9969602966</v>
+        <v>401830</v>
       </c>
       <c r="R4" t="n">
-        <v>6243324.773275147</v>
+        <v>6243325</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1011,19 +1003,9 @@
           <t>2016-04-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-04-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,59 +1056,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61726010</v>
+        <v>556247</v>
       </c>
       <c r="B5" t="n">
-        <v>77323</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91137</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>924</v>
+        <v>1541</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Fjällsopp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Strobilomyces strobilaceus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Scop.:Fr.) Berk.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandsjöholm, Sk</t>
+          <t>Vanåsfors norra, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>401829.9969602966</v>
+        <v>401736</v>
       </c>
       <c r="R5" t="n">
-        <v>6243324.773275147</v>
+        <v>6243501</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1150,22 +1130,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-04-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-09-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-04-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-09-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,95 +1152,68 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre bokskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturvårdsprogram Örkelljunga kommun</t>
-        </is>
-      </c>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61726011</v>
+        <v>61726009</v>
       </c>
       <c r="B6" t="n">
-        <v>75910</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med perithecier</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandsjöholm, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>401829.9969602966</v>
+        <v>401830</v>
       </c>
       <c r="R6" t="n">
-        <v>6243324.773275147</v>
+        <v>6243325</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1295,19 +1243,9 @@
           <t>2016-04-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-04-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1358,15 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>61726013</v>
+        <v>1321735</v>
       </c>
       <c r="B7" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,43 +1307,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>4786</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandsjöholm, Sk</t>
+          <t>Vanåsfors norra, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>401829.9969602966</v>
+        <v>401736</v>
       </c>
       <c r="R7" t="n">
-        <v>6243324.773275147</v>
+        <v>6243501</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1434,22 +1370,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2016-04-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-09-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2016-04-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-09-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,54 +1387,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre bokskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturvårdsprogram Örkelljunga kommun</t>
-        </is>
-      </c>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61726009</v>
+        <v>61726013</v>
       </c>
       <c r="B8" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1516,37 +1418,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandsjöholm, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>401829.9969602966</v>
+        <v>401830</v>
       </c>
       <c r="R8" t="n">
-        <v>6243324.773275147</v>
+        <v>6243325</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1576,19 +1481,9 @@
           <t>2016-04-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2016-04-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 47608-2022 artfynd.xlsx
+++ b/artfynd/A 47608-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
           <t>Naturvårdsprogram Örkelljunga kommun</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61726012</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
           <t>Naturvårdsprogram Örkelljunga kommun</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61726010</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1053,6 +1068,11 @@
           <t>Naturvårdsprogram Örkelljunga kommun</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61726011</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1169,6 +1189,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/556247</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1293,6 +1318,11 @@
           <t>Naturvårdsprogram Örkelljunga kommun</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61726009</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1404,6 +1434,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1321735</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1531,8 +1566,22 @@
           <t>Naturvårdsprogram Örkelljunga kommun</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61726013</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>